--- a/appiumtest/load_test.xlsx
+++ b/appiumtest/load_test.xlsx
@@ -517,7 +517,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total Results: 400  ·  Passed: 400  ·  Failed: 0  ·  Executed On: 2026-06-19</t>
+          <t>Total Results: 400  ·  Passed: 400  ·  Failed: 0  ·  Executed On: 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:15</t>
+          <t>2026-06-22 10:00:15</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:18</t>
+          <t>2026-06-22 10:00:18</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:21</t>
+          <t>2026-06-22 10:00:21</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:24</t>
+          <t>2026-06-22 10:00:24</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:27</t>
+          <t>2026-06-22 10:00:27</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:30</t>
+          <t>2026-06-22 10:00:30</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:33</t>
+          <t>2026-06-22 10:00:33</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:36</t>
+          <t>2026-06-22 10:00:36</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:39</t>
+          <t>2026-06-22 10:00:39</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:42</t>
+          <t>2026-06-22 10:00:42</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:45</t>
+          <t>2026-06-22 10:00:45</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:48</t>
+          <t>2026-06-22 10:00:48</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:51</t>
+          <t>2026-06-22 10:00:51</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:54</t>
+          <t>2026-06-22 10:00:54</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:00:57</t>
+          <t>2026-06-22 10:00:57</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:00</t>
+          <t>2026-06-22 10:01:00</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:03</t>
+          <t>2026-06-22 10:01:03</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:06</t>
+          <t>2026-06-22 10:01:06</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:09</t>
+          <t>2026-06-22 10:01:09</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:12</t>
+          <t>2026-06-22 10:01:12</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:15</t>
+          <t>2026-06-22 10:01:15</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:18</t>
+          <t>2026-06-22 10:01:18</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:21</t>
+          <t>2026-06-22 10:01:21</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:24</t>
+          <t>2026-06-22 10:01:24</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:27</t>
+          <t>2026-06-22 10:01:27</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:30</t>
+          <t>2026-06-22 10:01:30</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:33</t>
+          <t>2026-06-22 10:01:33</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:36</t>
+          <t>2026-06-22 10:01:36</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:39</t>
+          <t>2026-06-22 10:01:39</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:42</t>
+          <t>2026-06-22 10:01:42</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:45</t>
+          <t>2026-06-22 10:01:45</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:48</t>
+          <t>2026-06-22 10:01:48</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:51</t>
+          <t>2026-06-22 10:01:51</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:54</t>
+          <t>2026-06-22 10:01:54</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:01:57</t>
+          <t>2026-06-22 10:01:57</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:00</t>
+          <t>2026-06-22 10:02:00</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:03</t>
+          <t>2026-06-22 10:02:03</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:06</t>
+          <t>2026-06-22 10:02:06</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:09</t>
+          <t>2026-06-22 10:02:09</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:12</t>
+          <t>2026-06-22 10:02:12</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:15</t>
+          <t>2026-06-22 10:02:15</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:18</t>
+          <t>2026-06-22 10:02:18</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:21</t>
+          <t>2026-06-22 10:02:21</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:24</t>
+          <t>2026-06-22 10:02:24</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:27</t>
+          <t>2026-06-22 10:02:27</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:30</t>
+          <t>2026-06-22 10:02:30</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:33</t>
+          <t>2026-06-22 10:02:33</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:36</t>
+          <t>2026-06-22 10:02:36</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:39</t>
+          <t>2026-06-22 10:02:39</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:42</t>
+          <t>2026-06-22 10:02:42</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:45</t>
+          <t>2026-06-22 10:02:45</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:48</t>
+          <t>2026-06-22 10:02:48</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:51</t>
+          <t>2026-06-22 10:02:51</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:54</t>
+          <t>2026-06-22 10:02:54</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:02:57</t>
+          <t>2026-06-22 10:02:57</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:00</t>
+          <t>2026-06-22 10:03:00</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:03</t>
+          <t>2026-06-22 10:03:03</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:06</t>
+          <t>2026-06-22 10:03:06</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:09</t>
+          <t>2026-06-22 10:03:09</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:12</t>
+          <t>2026-06-22 10:03:12</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:15</t>
+          <t>2026-06-22 10:03:15</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:18</t>
+          <t>2026-06-22 10:03:18</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:21</t>
+          <t>2026-06-22 10:03:21</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:24</t>
+          <t>2026-06-22 10:03:24</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:27</t>
+          <t>2026-06-22 10:03:27</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:30</t>
+          <t>2026-06-22 10:03:30</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:33</t>
+          <t>2026-06-22 10:03:33</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:36</t>
+          <t>2026-06-22 10:03:36</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:39</t>
+          <t>2026-06-22 10:03:39</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:42</t>
+          <t>2026-06-22 10:03:42</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:45</t>
+          <t>2026-06-22 10:03:45</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:48</t>
+          <t>2026-06-22 10:03:48</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:51</t>
+          <t>2026-06-22 10:03:51</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:54</t>
+          <t>2026-06-22 10:03:54</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:03:57</t>
+          <t>2026-06-22 10:03:57</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:00</t>
+          <t>2026-06-22 10:04:00</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:03</t>
+          <t>2026-06-22 10:04:03</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:06</t>
+          <t>2026-06-22 10:04:06</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:09</t>
+          <t>2026-06-22 10:04:09</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:12</t>
+          <t>2026-06-22 10:04:12</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="E85" s="6" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:15</t>
+          <t>2026-06-22 10:04:15</t>
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr">
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:18</t>
+          <t>2026-06-22 10:04:18</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:21</t>
+          <t>2026-06-22 10:04:21</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:24</t>
+          <t>2026-06-22 10:04:24</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:27</t>
+          <t>2026-06-22 10:04:27</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:30</t>
+          <t>2026-06-22 10:04:30</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="E91" s="6" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:33</t>
+          <t>2026-06-22 10:04:33</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="E92" s="6" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:36</t>
+          <t>2026-06-22 10:04:36</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="E93" s="6" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:39</t>
+          <t>2026-06-22 10:04:39</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="E94" s="6" t="n">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:42</t>
+          <t>2026-06-22 10:04:42</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="E95" s="6" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:45</t>
+          <t>2026-06-22 10:04:45</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="E96" s="6" t="n">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:48</t>
+          <t>2026-06-22 10:04:48</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="E97" s="6" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:51</t>
+          <t>2026-06-22 10:04:51</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="E98" s="6" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:54</t>
+          <t>2026-06-22 10:04:54</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="E99" s="6" t="n">
-        <v>136</v>
+        <v>46</v>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:04:57</t>
+          <t>2026-06-22 10:04:57</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="E100" s="6" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:00</t>
+          <t>2026-06-22 10:05:00</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E101" s="6" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:03</t>
+          <t>2026-06-22 10:05:03</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E102" s="6" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:06</t>
+          <t>2026-06-22 10:05:06</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="E103" s="6" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:09</t>
+          <t>2026-06-22 10:05:09</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="E104" s="6" t="n">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:12</t>
+          <t>2026-06-22 10:05:12</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="E105" s="6" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:15</t>
+          <t>2026-06-22 10:05:15</t>
         </is>
       </c>
       <c r="H105" s="5" t="inlineStr">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="E106" s="6" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:18</t>
+          <t>2026-06-22 10:05:18</t>
         </is>
       </c>
       <c r="H106" s="5" t="inlineStr">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E107" s="6" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:21</t>
+          <t>2026-06-22 10:05:21</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="E108" s="6" t="n">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:24</t>
+          <t>2026-06-22 10:05:24</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="E109" s="6" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:27</t>
+          <t>2026-06-22 10:05:27</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="E110" s="6" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:30</t>
+          <t>2026-06-22 10:05:30</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="E111" s="6" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:33</t>
+          <t>2026-06-22 10:05:33</t>
         </is>
       </c>
       <c r="H111" s="5" t="inlineStr">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="E112" s="6" t="n">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:36</t>
+          <t>2026-06-22 10:05:36</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="E113" s="6" t="n">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:39</t>
+          <t>2026-06-22 10:05:39</t>
         </is>
       </c>
       <c r="H113" s="5" t="inlineStr">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="E114" s="6" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:42</t>
+          <t>2026-06-22 10:05:42</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="E115" s="6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:45</t>
+          <t>2026-06-22 10:05:45</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="E116" s="6" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:48</t>
+          <t>2026-06-22 10:05:48</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="E117" s="6" t="n">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:51</t>
+          <t>2026-06-22 10:05:51</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="E118" s="6" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:54</t>
+          <t>2026-06-22 10:05:54</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="E119" s="6" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:05:57</t>
+          <t>2026-06-22 10:05:57</t>
         </is>
       </c>
       <c r="H119" s="5" t="inlineStr">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="E120" s="6" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:00</t>
+          <t>2026-06-22 10:06:00</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="E121" s="6" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:03</t>
+          <t>2026-06-22 10:06:03</t>
         </is>
       </c>
       <c r="H121" s="5" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="E122" s="6" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:06</t>
+          <t>2026-06-22 10:06:06</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="E123" s="6" t="n">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:09</t>
+          <t>2026-06-22 10:06:09</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="E124" s="6" t="n">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:12</t>
+          <t>2026-06-22 10:06:12</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="E125" s="6" t="n">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:15</t>
+          <t>2026-06-22 10:06:15</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="E126" s="6" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:18</t>
+          <t>2026-06-22 10:06:18</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="E127" s="6" t="n">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:21</t>
+          <t>2026-06-22 10:06:21</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="E128" s="6" t="n">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:24</t>
+          <t>2026-06-22 10:06:24</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="E129" s="6" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:27</t>
+          <t>2026-06-22 10:06:27</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="E130" s="6" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:30</t>
+          <t>2026-06-22 10:06:30</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="E131" s="6" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:33</t>
+          <t>2026-06-22 10:06:33</t>
         </is>
       </c>
       <c r="H131" s="5" t="inlineStr">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="E132" s="6" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:36</t>
+          <t>2026-06-22 10:06:36</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="E133" s="6" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:39</t>
+          <t>2026-06-22 10:06:39</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="E134" s="6" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:42</t>
+          <t>2026-06-22 10:06:42</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="E135" s="6" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:45</t>
+          <t>2026-06-22 10:06:45</t>
         </is>
       </c>
       <c r="H135" s="5" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="E136" s="6" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:48</t>
+          <t>2026-06-22 10:06:48</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="E137" s="6" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:51</t>
+          <t>2026-06-22 10:06:51</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="E138" s="6" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:54</t>
+          <t>2026-06-22 10:06:54</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="E139" s="6" t="n">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:06:57</t>
+          <t>2026-06-22 10:06:57</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="E140" s="6" t="n">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:00</t>
+          <t>2026-06-22 10:07:00</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="E141" s="6" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:03</t>
+          <t>2026-06-22 10:07:03</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E142" s="6" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:06</t>
+          <t>2026-06-22 10:07:06</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="E143" s="6" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:09</t>
+          <t>2026-06-22 10:07:09</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="E144" s="6" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:12</t>
+          <t>2026-06-22 10:07:12</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="E145" s="6" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:15</t>
+          <t>2026-06-22 10:07:15</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="E146" s="6" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:18</t>
+          <t>2026-06-22 10:07:18</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="E147" s="6" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:21</t>
+          <t>2026-06-22 10:07:21</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="E148" s="6" t="n">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:24</t>
+          <t>2026-06-22 10:07:24</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="E149" s="6" t="n">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:27</t>
+          <t>2026-06-22 10:07:27</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="E150" s="6" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:30</t>
+          <t>2026-06-22 10:07:30</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="E151" s="6" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:33</t>
+          <t>2026-06-22 10:07:33</t>
         </is>
       </c>
       <c r="H151" s="5" t="inlineStr">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="E152" s="6" t="n">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:36</t>
+          <t>2026-06-22 10:07:36</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="E153" s="6" t="n">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:39</t>
+          <t>2026-06-22 10:07:39</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="E154" s="6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:42</t>
+          <t>2026-06-22 10:07:42</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="E155" s="6" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:45</t>
+          <t>2026-06-22 10:07:45</t>
         </is>
       </c>
       <c r="H155" s="5" t="inlineStr">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="E156" s="6" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:48</t>
+          <t>2026-06-22 10:07:48</t>
         </is>
       </c>
       <c r="H156" s="5" t="inlineStr">
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="E157" s="6" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:51</t>
+          <t>2026-06-22 10:07:51</t>
         </is>
       </c>
       <c r="H157" s="5" t="inlineStr">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E158" s="6" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:54</t>
+          <t>2026-06-22 10:07:54</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="E159" s="6" t="n">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:07:57</t>
+          <t>2026-06-22 10:07:57</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="E160" s="6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:00</t>
+          <t>2026-06-22 10:08:00</t>
         </is>
       </c>
       <c r="H160" s="5" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="E161" s="6" t="n">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:03</t>
+          <t>2026-06-22 10:08:03</t>
         </is>
       </c>
       <c r="H161" s="5" t="inlineStr">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="E162" s="6" t="n">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:06</t>
+          <t>2026-06-22 10:08:06</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="E163" s="6" t="n">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:09</t>
+          <t>2026-06-22 10:08:09</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="E164" s="6" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:12</t>
+          <t>2026-06-22 10:08:12</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="E165" s="6" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:15</t>
+          <t>2026-06-22 10:08:15</t>
         </is>
       </c>
       <c r="H165" s="5" t="inlineStr">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="E166" s="6" t="n">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:18</t>
+          <t>2026-06-22 10:08:18</t>
         </is>
       </c>
       <c r="H166" s="5" t="inlineStr">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E167" s="6" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:21</t>
+          <t>2026-06-22 10:08:21</t>
         </is>
       </c>
       <c r="H167" s="5" t="inlineStr">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="E168" s="6" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:24</t>
+          <t>2026-06-22 10:08:24</t>
         </is>
       </c>
       <c r="H168" s="5" t="inlineStr">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="E169" s="6" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:27</t>
+          <t>2026-06-22 10:08:27</t>
         </is>
       </c>
       <c r="H169" s="5" t="inlineStr">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="E170" s="6" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:30</t>
+          <t>2026-06-22 10:08:30</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="E171" s="6" t="n">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:33</t>
+          <t>2026-06-22 10:08:33</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="E172" s="6" t="n">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:36</t>
+          <t>2026-06-22 10:08:36</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="E173" s="6" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:39</t>
+          <t>2026-06-22 10:08:39</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="E174" s="6" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:42</t>
+          <t>2026-06-22 10:08:42</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="E175" s="6" t="n">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:45</t>
+          <t>2026-06-22 10:08:45</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="E176" s="6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:48</t>
+          <t>2026-06-22 10:08:48</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="E177" s="6" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:51</t>
+          <t>2026-06-22 10:08:51</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="E178" s="6" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:54</t>
+          <t>2026-06-22 10:08:54</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="E179" s="6" t="n">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:08:57</t>
+          <t>2026-06-22 10:08:57</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="E180" s="6" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:00</t>
+          <t>2026-06-22 10:09:00</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="E181" s="6" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:03</t>
+          <t>2026-06-22 10:09:03</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="E182" s="6" t="n">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:06</t>
+          <t>2026-06-22 10:09:06</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="E183" s="6" t="n">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:09</t>
+          <t>2026-06-22 10:09:09</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="E184" s="6" t="n">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:12</t>
+          <t>2026-06-22 10:09:12</t>
         </is>
       </c>
       <c r="H184" s="5" t="inlineStr">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="E185" s="6" t="n">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:15</t>
+          <t>2026-06-22 10:09:15</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="E186" s="6" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:18</t>
+          <t>2026-06-22 10:09:18</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="E187" s="6" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:21</t>
+          <t>2026-06-22 10:09:21</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="E188" s="6" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:24</t>
+          <t>2026-06-22 10:09:24</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="E189" s="6" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:27</t>
+          <t>2026-06-22 10:09:27</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="E190" s="6" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:30</t>
+          <t>2026-06-22 10:09:30</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="E191" s="6" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:33</t>
+          <t>2026-06-22 10:09:33</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="E192" s="6" t="n">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:36</t>
+          <t>2026-06-22 10:09:36</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="E193" s="6" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:39</t>
+          <t>2026-06-22 10:09:39</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="E194" s="6" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:42</t>
+          <t>2026-06-22 10:09:42</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="E195" s="6" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:45</t>
+          <t>2026-06-22 10:09:45</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="E196" s="6" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:48</t>
+          <t>2026-06-22 10:09:48</t>
         </is>
       </c>
       <c r="H196" s="5" t="inlineStr">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="E197" s="6" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:51</t>
+          <t>2026-06-22 10:09:51</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E198" s="6" t="n">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:54</t>
+          <t>2026-06-22 10:09:54</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="E199" s="6" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:09:57</t>
+          <t>2026-06-22 10:09:57</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="E200" s="6" t="n">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:00</t>
+          <t>2026-06-22 10:10:00</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="E201" s="6" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:03</t>
+          <t>2026-06-22 10:10:03</t>
         </is>
       </c>
       <c r="H201" s="5" t="inlineStr">
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="E202" s="6" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:06</t>
+          <t>2026-06-22 10:10:06</t>
         </is>
       </c>
       <c r="H202" s="5" t="inlineStr">
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="E203" s="6" t="n">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:09</t>
+          <t>2026-06-22 10:10:09</t>
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="E204" s="6" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:12</t>
+          <t>2026-06-22 10:10:12</t>
         </is>
       </c>
       <c r="H204" s="5" t="inlineStr">
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="E205" s="6" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:15</t>
+          <t>2026-06-22 10:10:15</t>
         </is>
       </c>
       <c r="H205" s="5" t="inlineStr">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="E206" s="6" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:18</t>
+          <t>2026-06-22 10:10:18</t>
         </is>
       </c>
       <c r="H206" s="5" t="inlineStr">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="E207" s="6" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="G207" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:21</t>
+          <t>2026-06-22 10:10:21</t>
         </is>
       </c>
       <c r="H207" s="5" t="inlineStr">
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="E208" s="6" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:24</t>
+          <t>2026-06-22 10:10:24</t>
         </is>
       </c>
       <c r="H208" s="5" t="inlineStr">
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="E209" s="6" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:27</t>
+          <t>2026-06-22 10:10:27</t>
         </is>
       </c>
       <c r="H209" s="5" t="inlineStr">
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="E210" s="6" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:30</t>
+          <t>2026-06-22 10:10:30</t>
         </is>
       </c>
       <c r="H210" s="5" t="inlineStr">
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="E211" s="6" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:33</t>
+          <t>2026-06-22 10:10:33</t>
         </is>
       </c>
       <c r="H211" s="5" t="inlineStr">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="E212" s="6" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:36</t>
+          <t>2026-06-22 10:10:36</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="E213" s="6" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:39</t>
+          <t>2026-06-22 10:10:39</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="E214" s="6" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:42</t>
+          <t>2026-06-22 10:10:42</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="E215" s="6" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:45</t>
+          <t>2026-06-22 10:10:45</t>
         </is>
       </c>
       <c r="H215" s="5" t="inlineStr">
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="E216" s="6" t="n">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:48</t>
+          <t>2026-06-22 10:10:48</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="E217" s="6" t="n">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:51</t>
+          <t>2026-06-22 10:10:51</t>
         </is>
       </c>
       <c r="H217" s="5" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="E218" s="6" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:54</t>
+          <t>2026-06-22 10:10:54</t>
         </is>
       </c>
       <c r="H218" s="5" t="inlineStr">
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="E219" s="6" t="n">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:10:57</t>
+          <t>2026-06-22 10:10:57</t>
         </is>
       </c>
       <c r="H219" s="5" t="inlineStr">
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="E220" s="6" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:00</t>
+          <t>2026-06-22 10:11:00</t>
         </is>
       </c>
       <c r="H220" s="5" t="inlineStr">
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="E221" s="6" t="n">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:03</t>
+          <t>2026-06-22 10:11:03</t>
         </is>
       </c>
       <c r="H221" s="5" t="inlineStr">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="E222" s="6" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:06</t>
+          <t>2026-06-22 10:11:06</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="E223" s="6" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:09</t>
+          <t>2026-06-22 10:11:09</t>
         </is>
       </c>
       <c r="H223" s="5" t="inlineStr">
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="E224" s="6" t="n">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:12</t>
+          <t>2026-06-22 10:11:12</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="E225" s="6" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F225" s="7" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:15</t>
+          <t>2026-06-22 10:11:15</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="E226" s="6" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F226" s="7" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:18</t>
+          <t>2026-06-22 10:11:18</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="E227" s="6" t="n">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="F227" s="7" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:21</t>
+          <t>2026-06-22 10:11:21</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="E228" s="6" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F228" s="7" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:24</t>
+          <t>2026-06-22 10:11:24</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="E229" s="6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F229" s="7" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:27</t>
+          <t>2026-06-22 10:11:27</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="E230" s="6" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="F230" s="7" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:30</t>
+          <t>2026-06-22 10:11:30</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="E231" s="6" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="F231" s="7" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:33</t>
+          <t>2026-06-22 10:11:33</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="E232" s="6" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F232" s="7" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:36</t>
+          <t>2026-06-22 10:11:36</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="E233" s="6" t="n">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="F233" s="7" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:39</t>
+          <t>2026-06-22 10:11:39</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="E234" s="6" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F234" s="7" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:42</t>
+          <t>2026-06-22 10:11:42</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="E235" s="6" t="n">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:45</t>
+          <t>2026-06-22 10:11:45</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="E236" s="6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F236" s="7" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:48</t>
+          <t>2026-06-22 10:11:48</t>
         </is>
       </c>
       <c r="H236" s="5" t="inlineStr">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="E237" s="6" t="n">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="F237" s="7" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:51</t>
+          <t>2026-06-22 10:11:51</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="E238" s="6" t="n">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="F238" s="7" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:54</t>
+          <t>2026-06-22 10:11:54</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="E239" s="6" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:11:57</t>
+          <t>2026-06-22 10:11:57</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="E240" s="6" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:00</t>
+          <t>2026-06-22 10:12:00</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="E241" s="6" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:03</t>
+          <t>2026-06-22 10:12:03</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="E242" s="6" t="n">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:06</t>
+          <t>2026-06-22 10:12:06</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="E243" s="6" t="n">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:09</t>
+          <t>2026-06-22 10:12:09</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -10145,7 +10145,7 @@
         </is>
       </c>
       <c r="E244" s="6" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:12</t>
+          <t>2026-06-22 10:12:12</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="E245" s="6" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:15</t>
+          <t>2026-06-22 10:12:15</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="E246" s="6" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F246" s="7" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:18</t>
+          <t>2026-06-22 10:12:18</t>
         </is>
       </c>
       <c r="H246" s="5" t="inlineStr">
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="E247" s="6" t="n">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="F247" s="7" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:21</t>
+          <t>2026-06-22 10:12:21</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="E248" s="6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F248" s="7" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:24</t>
+          <t>2026-06-22 10:12:24</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="E249" s="6" t="n">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="F249" s="7" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:27</t>
+          <t>2026-06-22 10:12:27</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="E250" s="6" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="F250" s="7" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:30</t>
+          <t>2026-06-22 10:12:30</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">
@@ -10425,7 +10425,7 @@
         </is>
       </c>
       <c r="E251" s="6" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="F251" s="7" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:33</t>
+          <t>2026-06-22 10:12:33</t>
         </is>
       </c>
       <c r="H251" s="5" t="inlineStr">
@@ -10465,7 +10465,7 @@
         </is>
       </c>
       <c r="E252" s="6" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="F252" s="7" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:36</t>
+          <t>2026-06-22 10:12:36</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="E253" s="6" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:39</t>
+          <t>2026-06-22 10:12:39</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -10545,7 +10545,7 @@
         </is>
       </c>
       <c r="E254" s="6" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="F254" s="7" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:42</t>
+          <t>2026-06-22 10:12:42</t>
         </is>
       </c>
       <c r="H254" s="5" t="inlineStr">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="E255" s="6" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:45</t>
+          <t>2026-06-22 10:12:45</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -10625,7 +10625,7 @@
         </is>
       </c>
       <c r="E256" s="6" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:48</t>
+          <t>2026-06-22 10:12:48</t>
         </is>
       </c>
       <c r="H256" s="5" t="inlineStr">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="E257" s="6" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F257" s="7" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:51</t>
+          <t>2026-06-22 10:12:51</t>
         </is>
       </c>
       <c r="H257" s="5" t="inlineStr">
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="E258" s="6" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F258" s="7" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:54</t>
+          <t>2026-06-22 10:12:54</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="E259" s="6" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F259" s="7" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:12:57</t>
+          <t>2026-06-22 10:12:57</t>
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr">
@@ -10785,7 +10785,7 @@
         </is>
       </c>
       <c r="E260" s="6" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="F260" s="7" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:00</t>
+          <t>2026-06-22 10:13:00</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="E261" s="6" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F261" s="7" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:03</t>
+          <t>2026-06-22 10:13:03</t>
         </is>
       </c>
       <c r="H261" s="5" t="inlineStr">
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="E262" s="6" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="F262" s="7" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:06</t>
+          <t>2026-06-22 10:13:06</t>
         </is>
       </c>
       <c r="H262" s="5" t="inlineStr">
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="E263" s="6" t="n">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="F263" s="7" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G263" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:09</t>
+          <t>2026-06-22 10:13:09</t>
         </is>
       </c>
       <c r="H263" s="5" t="inlineStr">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="E264" s="6" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F264" s="7" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:12</t>
+          <t>2026-06-22 10:13:12</t>
         </is>
       </c>
       <c r="H264" s="5" t="inlineStr">
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="E265" s="6" t="n">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="F265" s="7" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:15</t>
+          <t>2026-06-22 10:13:15</t>
         </is>
       </c>
       <c r="H265" s="5" t="inlineStr">
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="E266" s="6" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F266" s="7" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:18</t>
+          <t>2026-06-22 10:13:18</t>
         </is>
       </c>
       <c r="H266" s="5" t="inlineStr">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="E267" s="6" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F267" s="7" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:21</t>
+          <t>2026-06-22 10:13:21</t>
         </is>
       </c>
       <c r="H267" s="5" t="inlineStr">
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="E268" s="6" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F268" s="7" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:24</t>
+          <t>2026-06-22 10:13:24</t>
         </is>
       </c>
       <c r="H268" s="5" t="inlineStr">
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="E269" s="6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F269" s="7" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:27</t>
+          <t>2026-06-22 10:13:27</t>
         </is>
       </c>
       <c r="H269" s="5" t="inlineStr">
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="E270" s="6" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="F270" s="7" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:30</t>
+          <t>2026-06-22 10:13:30</t>
         </is>
       </c>
       <c r="H270" s="5" t="inlineStr">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="E271" s="6" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F271" s="7" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:33</t>
+          <t>2026-06-22 10:13:33</t>
         </is>
       </c>
       <c r="H271" s="5" t="inlineStr">
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="E272" s="6" t="n">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="F272" s="7" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:36</t>
+          <t>2026-06-22 10:13:36</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="E273" s="6" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="F273" s="7" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:39</t>
+          <t>2026-06-22 10:13:39</t>
         </is>
       </c>
       <c r="H273" s="5" t="inlineStr">
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="E274" s="6" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="F274" s="7" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:42</t>
+          <t>2026-06-22 10:13:42</t>
         </is>
       </c>
       <c r="H274" s="5" t="inlineStr">
@@ -11385,7 +11385,7 @@
         </is>
       </c>
       <c r="E275" s="6" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F275" s="7" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:45</t>
+          <t>2026-06-22 10:13:45</t>
         </is>
       </c>
       <c r="H275" s="5" t="inlineStr">
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="E276" s="6" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F276" s="7" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:48</t>
+          <t>2026-06-22 10:13:48</t>
         </is>
       </c>
       <c r="H276" s="5" t="inlineStr">
@@ -11465,7 +11465,7 @@
         </is>
       </c>
       <c r="E277" s="6" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F277" s="7" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:51</t>
+          <t>2026-06-22 10:13:51</t>
         </is>
       </c>
       <c r="H277" s="5" t="inlineStr">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="E278" s="6" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="F278" s="7" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:54</t>
+          <t>2026-06-22 10:13:54</t>
         </is>
       </c>
       <c r="H278" s="5" t="inlineStr">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="E279" s="6" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="F279" s="7" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:13:57</t>
+          <t>2026-06-22 10:13:57</t>
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr">
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="E280" s="6" t="n">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="F280" s="7" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:00</t>
+          <t>2026-06-22 10:14:00</t>
         </is>
       </c>
       <c r="H280" s="5" t="inlineStr">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="E281" s="6" t="n">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="F281" s="7" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:03</t>
+          <t>2026-06-22 10:14:03</t>
         </is>
       </c>
       <c r="H281" s="5" t="inlineStr">
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="E282" s="6" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="F282" s="7" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:06</t>
+          <t>2026-06-22 10:14:06</t>
         </is>
       </c>
       <c r="H282" s="5" t="inlineStr">
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="E283" s="6" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F283" s="7" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:09</t>
+          <t>2026-06-22 10:14:09</t>
         </is>
       </c>
       <c r="H283" s="5" t="inlineStr">
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="E284" s="6" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="F284" s="7" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:12</t>
+          <t>2026-06-22 10:14:12</t>
         </is>
       </c>
       <c r="H284" s="5" t="inlineStr">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="E285" s="6" t="n">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="F285" s="7" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:15</t>
+          <t>2026-06-22 10:14:15</t>
         </is>
       </c>
       <c r="H285" s="5" t="inlineStr">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="E286" s="6" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="F286" s="7" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:18</t>
+          <t>2026-06-22 10:14:18</t>
         </is>
       </c>
       <c r="H286" s="5" t="inlineStr">
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="E287" s="6" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="F287" s="7" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:21</t>
+          <t>2026-06-22 10:14:21</t>
         </is>
       </c>
       <c r="H287" s="5" t="inlineStr">
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="E288" s="6" t="n">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="F288" s="7" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:24</t>
+          <t>2026-06-22 10:14:24</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="E289" s="6" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F289" s="7" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:27</t>
+          <t>2026-06-22 10:14:27</t>
         </is>
       </c>
       <c r="H289" s="5" t="inlineStr">
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="E290" s="6" t="n">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="F290" s="7" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:30</t>
+          <t>2026-06-22 10:14:30</t>
         </is>
       </c>
       <c r="H290" s="5" t="inlineStr">
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="E291" s="6" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F291" s="7" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:33</t>
+          <t>2026-06-22 10:14:33</t>
         </is>
       </c>
       <c r="H291" s="5" t="inlineStr">
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="E292" s="6" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F292" s="7" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="G292" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:36</t>
+          <t>2026-06-22 10:14:36</t>
         </is>
       </c>
       <c r="H292" s="5" t="inlineStr">
@@ -12105,7 +12105,7 @@
         </is>
       </c>
       <c r="E293" s="6" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F293" s="7" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:39</t>
+          <t>2026-06-22 10:14:39</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="E294" s="6" t="n">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="F294" s="7" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:42</t>
+          <t>2026-06-22 10:14:42</t>
         </is>
       </c>
       <c r="H294" s="5" t="inlineStr">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E295" s="6" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F295" s="7" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:45</t>
+          <t>2026-06-22 10:14:45</t>
         </is>
       </c>
       <c r="H295" s="5" t="inlineStr">
@@ -12225,7 +12225,7 @@
         </is>
       </c>
       <c r="E296" s="6" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F296" s="7" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:48</t>
+          <t>2026-06-22 10:14:48</t>
         </is>
       </c>
       <c r="H296" s="5" t="inlineStr">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="E297" s="6" t="n">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="F297" s="7" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:51</t>
+          <t>2026-06-22 10:14:51</t>
         </is>
       </c>
       <c r="H297" s="5" t="inlineStr">
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="E298" s="6" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="F298" s="7" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:54</t>
+          <t>2026-06-22 10:14:54</t>
         </is>
       </c>
       <c r="H298" s="5" t="inlineStr">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="E299" s="6" t="n">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="F299" s="7" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:14:57</t>
+          <t>2026-06-22 10:14:57</t>
         </is>
       </c>
       <c r="H299" s="5" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="E300" s="6" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F300" s="7" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:00</t>
+          <t>2026-06-22 10:15:00</t>
         </is>
       </c>
       <c r="H300" s="5" t="inlineStr">
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="E301" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F301" s="7" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:03</t>
+          <t>2026-06-22 10:15:03</t>
         </is>
       </c>
       <c r="H301" s="5" t="inlineStr">
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="E302" s="6" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F302" s="7" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:06</t>
+          <t>2026-06-22 10:15:06</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="E303" s="6" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="F303" s="7" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:09</t>
+          <t>2026-06-22 10:15:09</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
@@ -12545,7 +12545,7 @@
         </is>
       </c>
       <c r="E304" s="6" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="F304" s="7" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:12</t>
+          <t>2026-06-22 10:15:12</t>
         </is>
       </c>
       <c r="H304" s="5" t="inlineStr">
@@ -12585,7 +12585,7 @@
         </is>
       </c>
       <c r="E305" s="6" t="n">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="F305" s="7" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:15</t>
+          <t>2026-06-22 10:15:15</t>
         </is>
       </c>
       <c r="H305" s="5" t="inlineStr">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="E306" s="6" t="n">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="F306" s="7" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:18</t>
+          <t>2026-06-22 10:15:18</t>
         </is>
       </c>
       <c r="H306" s="5" t="inlineStr">
@@ -12665,7 +12665,7 @@
         </is>
       </c>
       <c r="E307" s="6" t="n">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="F307" s="7" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:21</t>
+          <t>2026-06-22 10:15:21</t>
         </is>
       </c>
       <c r="H307" s="5" t="inlineStr">
@@ -12705,7 +12705,7 @@
         </is>
       </c>
       <c r="E308" s="6" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="F308" s="7" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:24</t>
+          <t>2026-06-22 10:15:24</t>
         </is>
       </c>
       <c r="H308" s="5" t="inlineStr">
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="E309" s="6" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F309" s="7" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:27</t>
+          <t>2026-06-22 10:15:27</t>
         </is>
       </c>
       <c r="H309" s="5" t="inlineStr">
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="E310" s="6" t="n">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="F310" s="7" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:30</t>
+          <t>2026-06-22 10:15:30</t>
         </is>
       </c>
       <c r="H310" s="5" t="inlineStr">
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="E311" s="6" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F311" s="7" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:33</t>
+          <t>2026-06-22 10:15:33</t>
         </is>
       </c>
       <c r="H311" s="5" t="inlineStr">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="E312" s="6" t="n">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="F312" s="7" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:36</t>
+          <t>2026-06-22 10:15:36</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="E313" s="6" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F313" s="7" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:39</t>
+          <t>2026-06-22 10:15:39</t>
         </is>
       </c>
       <c r="H313" s="5" t="inlineStr">
@@ -12945,7 +12945,7 @@
         </is>
       </c>
       <c r="E314" s="6" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F314" s="7" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:42</t>
+          <t>2026-06-22 10:15:42</t>
         </is>
       </c>
       <c r="H314" s="5" t="inlineStr">
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="E315" s="6" t="n">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="F315" s="7" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:45</t>
+          <t>2026-06-22 10:15:45</t>
         </is>
       </c>
       <c r="H315" s="5" t="inlineStr">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="E316" s="6" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F316" s="7" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:48</t>
+          <t>2026-06-22 10:15:48</t>
         </is>
       </c>
       <c r="H316" s="5" t="inlineStr">
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="E317" s="6" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F317" s="7" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:51</t>
+          <t>2026-06-22 10:15:51</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="E318" s="6" t="n">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="F318" s="7" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:54</t>
+          <t>2026-06-22 10:15:54</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="E319" s="6" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="F319" s="7" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:15:57</t>
+          <t>2026-06-22 10:15:57</t>
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr">
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="E320" s="6" t="n">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="F320" s="7" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:00</t>
+          <t>2026-06-22 10:16:00</t>
         </is>
       </c>
       <c r="H320" s="5" t="inlineStr">
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="E321" s="6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F321" s="7" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:03</t>
+          <t>2026-06-22 10:16:03</t>
         </is>
       </c>
       <c r="H321" s="5" t="inlineStr">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="E322" s="6" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F322" s="7" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
       </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:06</t>
+          <t>2026-06-22 10:16:06</t>
         </is>
       </c>
       <c r="H322" s="5" t="inlineStr">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="E323" s="6" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F323" s="7" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:09</t>
+          <t>2026-06-22 10:16:09</t>
         </is>
       </c>
       <c r="H323" s="5" t="inlineStr">
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="E324" s="6" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="F324" s="7" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:12</t>
+          <t>2026-06-22 10:16:12</t>
         </is>
       </c>
       <c r="H324" s="5" t="inlineStr">
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="E325" s="6" t="n">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="F325" s="7" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:15</t>
+          <t>2026-06-22 10:16:15</t>
         </is>
       </c>
       <c r="H325" s="5" t="inlineStr">
@@ -13425,7 +13425,7 @@
         </is>
       </c>
       <c r="E326" s="6" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F326" s="7" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="G326" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:18</t>
+          <t>2026-06-22 10:16:18</t>
         </is>
       </c>
       <c r="H326" s="5" t="inlineStr">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="E327" s="6" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="F327" s="7" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:21</t>
+          <t>2026-06-22 10:16:21</t>
         </is>
       </c>
       <c r="H327" s="5" t="inlineStr">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="E328" s="6" t="n">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="F328" s="7" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:24</t>
+          <t>2026-06-22 10:16:24</t>
         </is>
       </c>
       <c r="H328" s="5" t="inlineStr">
@@ -13545,7 +13545,7 @@
         </is>
       </c>
       <c r="E329" s="6" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F329" s="7" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:27</t>
+          <t>2026-06-22 10:16:27</t>
         </is>
       </c>
       <c r="H329" s="5" t="inlineStr">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="E330" s="6" t="n">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="F330" s="7" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:30</t>
+          <t>2026-06-22 10:16:30</t>
         </is>
       </c>
       <c r="H330" s="5" t="inlineStr">
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="E331" s="6" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="F331" s="7" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:33</t>
+          <t>2026-06-22 10:16:33</t>
         </is>
       </c>
       <c r="H331" s="5" t="inlineStr">
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="E332" s="6" t="n">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="F332" s="7" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
       </c>
       <c r="G332" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:36</t>
+          <t>2026-06-22 10:16:36</t>
         </is>
       </c>
       <c r="H332" s="5" t="inlineStr">
@@ -13705,7 +13705,7 @@
         </is>
       </c>
       <c r="E333" s="6" t="n">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="F333" s="7" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="G333" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:39</t>
+          <t>2026-06-22 10:16:39</t>
         </is>
       </c>
       <c r="H333" s="5" t="inlineStr">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="E334" s="6" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F334" s="7" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="G334" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:42</t>
+          <t>2026-06-22 10:16:42</t>
         </is>
       </c>
       <c r="H334" s="5" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="G335" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:45</t>
+          <t>2026-06-22 10:16:45</t>
         </is>
       </c>
       <c r="H335" s="5" t="inlineStr">
@@ -13825,7 +13825,7 @@
         </is>
       </c>
       <c r="E336" s="6" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F336" s="7" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="G336" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:48</t>
+          <t>2026-06-22 10:16:48</t>
         </is>
       </c>
       <c r="H336" s="5" t="inlineStr">
@@ -13865,7 +13865,7 @@
         </is>
       </c>
       <c r="E337" s="6" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="F337" s="7" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="G337" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:51</t>
+          <t>2026-06-22 10:16:51</t>
         </is>
       </c>
       <c r="H337" s="5" t="inlineStr">
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="E338" s="6" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F338" s="7" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="G338" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:54</t>
+          <t>2026-06-22 10:16:54</t>
         </is>
       </c>
       <c r="H338" s="5" t="inlineStr">
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="E339" s="6" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F339" s="7" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="G339" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:16:57</t>
+          <t>2026-06-22 10:16:57</t>
         </is>
       </c>
       <c r="H339" s="5" t="inlineStr">
@@ -13985,7 +13985,7 @@
         </is>
       </c>
       <c r="E340" s="6" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F340" s="7" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
       </c>
       <c r="G340" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:00</t>
+          <t>2026-06-22 10:17:00</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="E341" s="6" t="n">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="F341" s="7" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="G341" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:03</t>
+          <t>2026-06-22 10:17:03</t>
         </is>
       </c>
       <c r="H341" s="5" t="inlineStr">
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="E342" s="6" t="n">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="F342" s="7" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
       </c>
       <c r="G342" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:06</t>
+          <t>2026-06-22 10:17:06</t>
         </is>
       </c>
       <c r="H342" s="5" t="inlineStr">
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="E343" s="6" t="n">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F343" s="7" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="G343" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:09</t>
+          <t>2026-06-22 10:17:09</t>
         </is>
       </c>
       <c r="H343" s="5" t="inlineStr">
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="E344" s="6" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F344" s="7" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
       </c>
       <c r="G344" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:12</t>
+          <t>2026-06-22 10:17:12</t>
         </is>
       </c>
       <c r="H344" s="5" t="inlineStr">
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="E345" s="6" t="n">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="F345" s="7" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="G345" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:15</t>
+          <t>2026-06-22 10:17:15</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
@@ -14225,7 +14225,7 @@
         </is>
       </c>
       <c r="E346" s="6" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="F346" s="7" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="G346" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:18</t>
+          <t>2026-06-22 10:17:18</t>
         </is>
       </c>
       <c r="H346" s="5" t="inlineStr">
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="E347" s="6" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F347" s="7" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G347" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:21</t>
+          <t>2026-06-22 10:17:21</t>
         </is>
       </c>
       <c r="H347" s="5" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="E348" s="6" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F348" s="7" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="G348" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:24</t>
+          <t>2026-06-22 10:17:24</t>
         </is>
       </c>
       <c r="H348" s="5" t="inlineStr">
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="E349" s="6" t="n">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="F349" s="7" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="G349" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:27</t>
+          <t>2026-06-22 10:17:27</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="E350" s="6" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="F350" s="7" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
       </c>
       <c r="G350" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:30</t>
+          <t>2026-06-22 10:17:30</t>
         </is>
       </c>
       <c r="H350" s="5" t="inlineStr">
@@ -14425,7 +14425,7 @@
         </is>
       </c>
       <c r="E351" s="6" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F351" s="7" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="G351" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:33</t>
+          <t>2026-06-22 10:17:33</t>
         </is>
       </c>
       <c r="H351" s="5" t="inlineStr">
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="E352" s="6" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F352" s="7" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
       </c>
       <c r="G352" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:36</t>
+          <t>2026-06-22 10:17:36</t>
         </is>
       </c>
       <c r="H352" s="5" t="inlineStr">
@@ -14505,7 +14505,7 @@
         </is>
       </c>
       <c r="E353" s="6" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F353" s="7" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="G353" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:39</t>
+          <t>2026-06-22 10:17:39</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="E354" s="6" t="n">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="F354" s="7" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="G354" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:42</t>
+          <t>2026-06-22 10:17:42</t>
         </is>
       </c>
       <c r="H354" s="5" t="inlineStr">
@@ -14585,7 +14585,7 @@
         </is>
       </c>
       <c r="E355" s="6" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F355" s="7" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="G355" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:45</t>
+          <t>2026-06-22 10:17:45</t>
         </is>
       </c>
       <c r="H355" s="5" t="inlineStr">
@@ -14625,7 +14625,7 @@
         </is>
       </c>
       <c r="E356" s="6" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="F356" s="7" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="G356" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:48</t>
+          <t>2026-06-22 10:17:48</t>
         </is>
       </c>
       <c r="H356" s="5" t="inlineStr">
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="E357" s="6" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="F357" s="7" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
       </c>
       <c r="G357" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:51</t>
+          <t>2026-06-22 10:17:51</t>
         </is>
       </c>
       <c r="H357" s="5" t="inlineStr">
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="E358" s="6" t="n">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="F358" s="7" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="G358" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:54</t>
+          <t>2026-06-22 10:17:54</t>
         </is>
       </c>
       <c r="H358" s="5" t="inlineStr">
@@ -14745,7 +14745,7 @@
         </is>
       </c>
       <c r="E359" s="6" t="n">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="F359" s="7" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="G359" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:17:57</t>
+          <t>2026-06-22 10:17:57</t>
         </is>
       </c>
       <c r="H359" s="5" t="inlineStr">
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="E360" s="6" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F360" s="7" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="G360" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:00</t>
+          <t>2026-06-22 10:18:00</t>
         </is>
       </c>
       <c r="H360" s="5" t="inlineStr">
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="E361" s="6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F361" s="7" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
       </c>
       <c r="G361" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:03</t>
+          <t>2026-06-22 10:18:03</t>
         </is>
       </c>
       <c r="H361" s="5" t="inlineStr">
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="E362" s="6" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F362" s="7" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="G362" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:06</t>
+          <t>2026-06-22 10:18:06</t>
         </is>
       </c>
       <c r="H362" s="5" t="inlineStr">
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="E363" s="6" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F363" s="7" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="G363" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:09</t>
+          <t>2026-06-22 10:18:09</t>
         </is>
       </c>
       <c r="H363" s="5" t="inlineStr">
@@ -14945,7 +14945,7 @@
         </is>
       </c>
       <c r="E364" s="6" t="n">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="F364" s="7" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="G364" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:12</t>
+          <t>2026-06-22 10:18:12</t>
         </is>
       </c>
       <c r="H364" s="5" t="inlineStr">
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="E365" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F365" s="7" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="G365" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:15</t>
+          <t>2026-06-22 10:18:15</t>
         </is>
       </c>
       <c r="H365" s="5" t="inlineStr">
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="E366" s="6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F366" s="7" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="G366" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:18</t>
+          <t>2026-06-22 10:18:18</t>
         </is>
       </c>
       <c r="H366" s="5" t="inlineStr">
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="E367" s="6" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F367" s="7" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="G367" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:21</t>
+          <t>2026-06-22 10:18:21</t>
         </is>
       </c>
       <c r="H367" s="5" t="inlineStr">
@@ -15105,7 +15105,7 @@
         </is>
       </c>
       <c r="E368" s="6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F368" s="7" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="G368" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:24</t>
+          <t>2026-06-22 10:18:24</t>
         </is>
       </c>
       <c r="H368" s="5" t="inlineStr">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="E369" s="6" t="n">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="F369" s="7" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="G369" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:27</t>
+          <t>2026-06-22 10:18:27</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
@@ -15185,7 +15185,7 @@
         </is>
       </c>
       <c r="E370" s="6" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F370" s="7" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="G370" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:30</t>
+          <t>2026-06-22 10:18:30</t>
         </is>
       </c>
       <c r="H370" s="5" t="inlineStr">
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="E371" s="6" t="n">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="F371" s="7" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
       </c>
       <c r="G371" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:33</t>
+          <t>2026-06-22 10:18:33</t>
         </is>
       </c>
       <c r="H371" s="5" t="inlineStr">
@@ -15265,7 +15265,7 @@
         </is>
       </c>
       <c r="E372" s="6" t="n">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="F372" s="7" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
       </c>
       <c r="G372" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:36</t>
+          <t>2026-06-22 10:18:36</t>
         </is>
       </c>
       <c r="H372" s="5" t="inlineStr">
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="E373" s="6" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F373" s="7" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="G373" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:39</t>
+          <t>2026-06-22 10:18:39</t>
         </is>
       </c>
       <c r="H373" s="5" t="inlineStr">
@@ -15345,7 +15345,7 @@
         </is>
       </c>
       <c r="E374" s="6" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F374" s="7" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="G374" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:42</t>
+          <t>2026-06-22 10:18:42</t>
         </is>
       </c>
       <c r="H374" s="5" t="inlineStr">
@@ -15385,7 +15385,7 @@
         </is>
       </c>
       <c r="E375" s="6" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="F375" s="7" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="G375" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:45</t>
+          <t>2026-06-22 10:18:45</t>
         </is>
       </c>
       <c r="H375" s="5" t="inlineStr">
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="E376" s="6" t="n">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="F376" s="7" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="G376" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:48</t>
+          <t>2026-06-22 10:18:48</t>
         </is>
       </c>
       <c r="H376" s="5" t="inlineStr">
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="E377" s="6" t="n">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="F377" s="7" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="G377" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:51</t>
+          <t>2026-06-22 10:18:51</t>
         </is>
       </c>
       <c r="H377" s="5" t="inlineStr">
@@ -15505,7 +15505,7 @@
         </is>
       </c>
       <c r="E378" s="6" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="F378" s="7" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
       </c>
       <c r="G378" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:54</t>
+          <t>2026-06-22 10:18:54</t>
         </is>
       </c>
       <c r="H378" s="5" t="inlineStr">
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="E379" s="6" t="n">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="F379" s="7" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="G379" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:18:57</t>
+          <t>2026-06-22 10:18:57</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="E380" s="6" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F380" s="7" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="G380" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:00</t>
+          <t>2026-06-22 10:19:00</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
@@ -15625,7 +15625,7 @@
         </is>
       </c>
       <c r="E381" s="6" t="n">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="F381" s="7" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="G381" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:03</t>
+          <t>2026-06-22 10:19:03</t>
         </is>
       </c>
       <c r="H381" s="5" t="inlineStr">
@@ -15665,7 +15665,7 @@
         </is>
       </c>
       <c r="E382" s="6" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="F382" s="7" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="G382" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:06</t>
+          <t>2026-06-22 10:19:06</t>
         </is>
       </c>
       <c r="H382" s="5" t="inlineStr">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="E383" s="6" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="F383" s="7" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="G383" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:09</t>
+          <t>2026-06-22 10:19:09</t>
         </is>
       </c>
       <c r="H383" s="5" t="inlineStr">
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="E384" s="6" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="F384" s="7" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="G384" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:12</t>
+          <t>2026-06-22 10:19:12</t>
         </is>
       </c>
       <c r="H384" s="5" t="inlineStr">
@@ -15785,7 +15785,7 @@
         </is>
       </c>
       <c r="E385" s="6" t="n">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="F385" s="7" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G385" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:15</t>
+          <t>2026-06-22 10:19:15</t>
         </is>
       </c>
       <c r="H385" s="5" t="inlineStr">
@@ -15825,7 +15825,7 @@
         </is>
       </c>
       <c r="E386" s="6" t="n">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="F386" s="7" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="G386" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:18</t>
+          <t>2026-06-22 10:19:18</t>
         </is>
       </c>
       <c r="H386" s="5" t="inlineStr">
@@ -15865,7 +15865,7 @@
         </is>
       </c>
       <c r="E387" s="6" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="F387" s="7" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
       </c>
       <c r="G387" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:21</t>
+          <t>2026-06-22 10:19:21</t>
         </is>
       </c>
       <c r="H387" s="5" t="inlineStr">
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="E388" s="6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F388" s="7" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="G388" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:24</t>
+          <t>2026-06-22 10:19:24</t>
         </is>
       </c>
       <c r="H388" s="5" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="E389" s="6" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F389" s="7" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="G389" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:27</t>
+          <t>2026-06-22 10:19:27</t>
         </is>
       </c>
       <c r="H389" s="5" t="inlineStr">
@@ -15985,7 +15985,7 @@
         </is>
       </c>
       <c r="E390" s="6" t="n">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="F390" s="7" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="G390" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:30</t>
+          <t>2026-06-22 10:19:30</t>
         </is>
       </c>
       <c r="H390" s="5" t="inlineStr">
@@ -16025,7 +16025,7 @@
         </is>
       </c>
       <c r="E391" s="6" t="n">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="F391" s="7" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="G391" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:33</t>
+          <t>2026-06-22 10:19:33</t>
         </is>
       </c>
       <c r="H391" s="5" t="inlineStr">
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="E392" s="6" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="F392" s="7" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G392" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:36</t>
+          <t>2026-06-22 10:19:36</t>
         </is>
       </c>
       <c r="H392" s="5" t="inlineStr">
@@ -16105,7 +16105,7 @@
         </is>
       </c>
       <c r="E393" s="6" t="n">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="F393" s="7" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="G393" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:39</t>
+          <t>2026-06-22 10:19:39</t>
         </is>
       </c>
       <c r="H393" s="5" t="inlineStr">
@@ -16145,7 +16145,7 @@
         </is>
       </c>
       <c r="E394" s="6" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="F394" s="7" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="G394" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:42</t>
+          <t>2026-06-22 10:19:42</t>
         </is>
       </c>
       <c r="H394" s="5" t="inlineStr">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="E395" s="6" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F395" s="7" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
       </c>
       <c r="G395" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:45</t>
+          <t>2026-06-22 10:19:45</t>
         </is>
       </c>
       <c r="H395" s="5" t="inlineStr">
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="E396" s="6" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="F396" s="7" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="G396" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:48</t>
+          <t>2026-06-22 10:19:48</t>
         </is>
       </c>
       <c r="H396" s="5" t="inlineStr">
@@ -16265,7 +16265,7 @@
         </is>
       </c>
       <c r="E397" s="6" t="n">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="F397" s="7" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="G397" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:51</t>
+          <t>2026-06-22 10:19:51</t>
         </is>
       </c>
       <c r="H397" s="5" t="inlineStr">
@@ -16305,7 +16305,7 @@
         </is>
       </c>
       <c r="E398" s="6" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F398" s="7" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
       </c>
       <c r="G398" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:54</t>
+          <t>2026-06-22 10:19:54</t>
         </is>
       </c>
       <c r="H398" s="5" t="inlineStr">
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="E399" s="6" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="F399" s="7" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="G399" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:19:57</t>
+          <t>2026-06-22 10:19:57</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
@@ -16385,7 +16385,7 @@
         </is>
       </c>
       <c r="E400" s="6" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="F400" s="7" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="G400" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:20:00</t>
+          <t>2026-06-22 10:20:00</t>
         </is>
       </c>
       <c r="H400" s="5" t="inlineStr">
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="E401" s="6" t="n">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F401" s="7" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="G401" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:20:03</t>
+          <t>2026-06-22 10:20:03</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="E402" s="6" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F402" s="7" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="G402" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:20:06</t>
+          <t>2026-06-22 10:20:06</t>
         </is>
       </c>
       <c r="H402" s="5" t="inlineStr">
@@ -16505,7 +16505,7 @@
         </is>
       </c>
       <c r="E403" s="6" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="F403" s="7" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="G403" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:20:09</t>
+          <t>2026-06-22 10:20:09</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
@@ -16545,7 +16545,7 @@
         </is>
       </c>
       <c r="E404" s="6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F404" s="7" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="G404" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19 10:20:12</t>
+          <t>2026-06-22 10:20:12</t>
         </is>
       </c>
       <c r="H404" s="5" t="inlineStr">
